--- a/final_data_pipeline/output/312120longform_elec_options_nowhp.xlsx
+++ b/final_data_pipeline/output/312120longform_elec_options_nowhp.xlsx
@@ -688,7 +688,7 @@
         <v>44</v>
       </c>
       <c r="I4">
-        <v>10</v>
+        <v>17.71296296296294</v>
       </c>
       <c r="J4">
         <v>8000</v>
@@ -703,10 +703,10 @@
         <v>1085506.970789521</v>
       </c>
       <c r="N4">
-        <v>1.741590909090909</v>
+        <v>1.872915723725898</v>
       </c>
       <c r="O4">
-        <v>1.89075</v>
+        <v>2.048770944115581</v>
       </c>
       <c r="P4">
         <v>135.6883713486901</v>
@@ -741,7 +741,7 @@
         <v>45</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>17.71296296296294</v>
       </c>
       <c r="J5">
         <v>8000</v>
@@ -788,7 +788,7 @@
         <v>44</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="J6">
         <v>8000</v>
@@ -803,10 +803,10 @@
         <v>439263.8545030078</v>
       </c>
       <c r="N6">
-        <v>1.741590909090909</v>
+        <v>1.572614297115494</v>
       </c>
       <c r="O6">
-        <v>1.89075</v>
+        <v>1.690895540926593</v>
       </c>
       <c r="P6">
         <v>54.90798181287597</v>
@@ -1347,7 +1347,7 @@
         <v>44</v>
       </c>
       <c r="I17">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="J17">
         <v>8000</v>
@@ -1362,10 +1362,10 @@
         <v>538259.7276283206</v>
       </c>
       <c r="N17">
-        <v>1.741590909090909</v>
+        <v>1.586359976998275</v>
       </c>
       <c r="O17">
-        <v>1.89075</v>
+        <v>1.707009404388715</v>
       </c>
       <c r="P17">
         <v>67.28246595354007</v>
@@ -1500,7 +1500,7 @@
         <v>44</v>
       </c>
       <c r="I20">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="J20">
         <v>8000</v>
@@ -1515,10 +1515,10 @@
         <v>3376861.685603743</v>
       </c>
       <c r="N20">
-        <v>1.741590909090909</v>
+        <v>1.586359976998275</v>
       </c>
       <c r="O20">
-        <v>1.89075</v>
+        <v>1.707009404388715</v>
       </c>
       <c r="P20">
         <v>422.1077107004679</v>
@@ -1806,7 +1806,7 @@
         <v>44</v>
       </c>
       <c r="I26">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="J26">
         <v>8000</v>
@@ -1821,10 +1821,10 @@
         <v>281488.4824294684</v>
       </c>
       <c r="N26">
-        <v>1.741590909090909</v>
+        <v>1.572614297115494</v>
       </c>
       <c r="O26">
-        <v>1.89075</v>
+        <v>1.690895540926593</v>
       </c>
       <c r="P26">
         <v>35.18606030368355</v>
@@ -1859,7 +1859,7 @@
         <v>45</v>
       </c>
       <c r="I27">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="J27">
         <v>8000</v>
